--- a/AO 2025.xlsx
+++ b/AO 2025.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7be5388bb47206f7/Desktop/ML/ML-Tennis-Prediction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{E15961E4-1683-446E-89A5-E399F4FDA100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DEB2C4F-4232-4018-9FFF-C265FF4C0062}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A907DE4-5B45-4024-8DF4-677F5AA34994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{ABE403E4-F928-4BC5-BD17-2E042ACD4338}"/>
+    <workbookView xWindow="4680" yWindow="936" windowWidth="17280" windowHeight="8880" xr2:uid="{ABE403E4-F928-4BC5-BD17-2E042ACD4338}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="AO 2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="136">
   <si>
     <t>p1_name</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Alexander Bublik</t>
   </si>
   <si>
-    <t>Facundo Diaz Acost</t>
-  </si>
-  <si>
     <t>Zizou Bergs</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
     <t>Federico Coria</t>
   </si>
   <si>
-    <t>Botic Van De Zan</t>
-  </si>
-  <si>
     <t>Alex De Minaur</t>
   </si>
   <si>
@@ -155,15 +149,9 @@
     <t>Francisco Comesana</t>
   </si>
   <si>
-    <t>Altmaier Daniel</t>
-  </si>
-  <si>
     <t>Gael Monfils</t>
   </si>
   <si>
-    <t>Giovanni Mpetshi Pe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ben Shelton </t>
   </si>
   <si>
@@ -173,9 +161,6 @@
     <t>Kamil Majchrzak</t>
   </si>
   <si>
-    <t>Dennis Shapovalov</t>
-  </si>
-  <si>
     <t>Matteo Arnaldi</t>
   </si>
   <si>
@@ -194,15 +179,9 @@
     <t>Stan Wawrinka</t>
   </si>
   <si>
-    <t>Thiago Seyboth Wi</t>
-  </si>
-  <si>
     <t>Fabian Marozsan</t>
   </si>
   <si>
-    <t>Arthur Rinderknec</t>
-  </si>
-  <si>
     <t>Frances Tiafoe</t>
   </si>
   <si>
@@ -218,9 +197,6 @@
     <t>Mitchell Krueger</t>
   </si>
   <si>
-    <t>Camilo Ugo Carabe</t>
-  </si>
-  <si>
     <t>Learner Tien</t>
   </si>
   <si>
@@ -233,12 +209,6 @@
     <t>Novak Djokovic</t>
   </si>
   <si>
-    <t>Nishesh Basavaredd</t>
-  </si>
-  <si>
-    <t>Jamie Faria</t>
-  </si>
-  <si>
     <t>Pavel Kotov</t>
   </si>
   <si>
@@ -287,9 +257,6 @@
     <t>Thanasi Kokkinakis</t>
   </si>
   <si>
-    <t>Romn Safiullin</t>
-  </si>
-  <si>
     <t>Damir Dzumhur</t>
   </si>
   <si>
@@ -332,9 +299,6 @@
     <t>Jaume Munar</t>
   </si>
   <si>
-    <t>Nikoloz Basilashvi</t>
-  </si>
-  <si>
     <t>Jakub Mensik</t>
   </si>
   <si>
@@ -344,9 +308,6 @@
     <t>Jan Lennard Struff</t>
   </si>
   <si>
-    <t>Felix Auger Aliassimme</t>
-  </si>
-  <si>
     <t>Alejandro Tabilo</t>
   </si>
   <si>
@@ -359,9 +320,6 @@
     <t>Thiago Monteiro</t>
   </si>
   <si>
-    <t>Christopher Oconnel</t>
-  </si>
-  <si>
     <t>Tommy Paul</t>
   </si>
   <si>
@@ -374,9 +332,6 @@
     <t>Hady Habib</t>
   </si>
   <si>
-    <t>Yunchaokete Bu</t>
-  </si>
-  <si>
     <t>Adam Walton</t>
   </si>
   <si>
@@ -449,9 +404,6 @@
     <t>Alejandro Davidovich Fokina</t>
   </si>
   <si>
-    <t>Stefanos Michelsen</t>
-  </si>
-  <si>
     <t>Ben Shelton</t>
   </si>
   <si>
@@ -459,6 +411,39 @@
   </si>
   <si>
     <t xml:space="preserve">target </t>
+  </si>
+  <si>
+    <t>Thiago Seyboth Wild</t>
+  </si>
+  <si>
+    <t>Felix Auger Aliassime</t>
+  </si>
+  <si>
+    <t>Giovanni Mpetshi Perricard</t>
+  </si>
+  <si>
+    <t>Arthur Rinderknech</t>
+  </si>
+  <si>
+    <t>Christopher Oconnell</t>
+  </si>
+  <si>
+    <t>Nikoloz Basilashvili</t>
+  </si>
+  <si>
+    <t>Botic Van De Zandschulp</t>
+  </si>
+  <si>
+    <t>Nishesh Basavareddy</t>
+  </si>
+  <si>
+    <t>Roman Safiullin</t>
+  </si>
+  <si>
+    <t>Camilo Ugo Carabelli</t>
+  </si>
+  <si>
+    <t>Bu Yunchaokete</t>
   </si>
 </sst>
 </file>
@@ -520,6 +505,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -857,7 +846,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -904,7 +893,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1044,10 +1033,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1058,10 +1047,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1072,10 +1061,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1086,10 +1075,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1100,10 +1089,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1114,10 +1103,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1128,10 +1117,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1142,10 +1131,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1156,10 +1145,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1170,10 +1159,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1184,10 +1173,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1198,10 +1187,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1212,10 +1201,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1226,10 +1215,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1240,10 +1229,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1254,10 +1243,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1268,10 +1257,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1282,10 +1271,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1296,10 +1285,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1310,10 +1299,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1324,10 +1313,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1338,10 +1327,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1352,10 +1341,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1366,10 +1355,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1380,10 +1369,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1394,10 +1383,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1408,10 +1397,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1422,10 +1411,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -1436,10 +1425,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1450,10 +1439,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1464,10 +1453,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1478,10 +1467,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1492,10 +1481,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1506,10 +1495,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1520,10 +1509,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1534,10 +1523,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1548,10 +1537,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -1562,10 +1551,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1576,10 +1565,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1590,10 +1579,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1604,10 +1593,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1618,10 +1607,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -1632,10 +1621,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -1646,10 +1635,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1660,10 +1649,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -1674,10 +1663,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -1688,10 +1677,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -1702,10 +1691,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -1716,10 +1705,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1730,10 +1719,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -1744,10 +1733,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -1775,7 +1764,7 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -1845,7 +1834,7 @@
         <v>26</v>
       </c>
       <c r="B72" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -1856,10 +1845,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C73">
         <v>2</v>
@@ -1870,10 +1859,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C74">
         <v>2</v>
@@ -1884,10 +1873,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -1898,10 +1887,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -1912,10 +1901,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B77" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C77">
         <v>2</v>
@@ -1926,10 +1915,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B78" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -1940,10 +1929,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B79" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -1954,10 +1943,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B80" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -1968,10 +1957,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B81" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -1982,10 +1971,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -1996,10 +1985,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -2010,10 +1999,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -2024,10 +2013,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -2038,10 +2027,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C86">
         <v>2</v>
@@ -2052,10 +2041,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -2066,10 +2055,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C88">
         <v>2</v>
@@ -2080,10 +2069,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -2094,10 +2083,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -2108,10 +2097,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C91">
         <v>2</v>
@@ -2122,10 +2111,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B92" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -2136,10 +2125,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B93" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -2150,10 +2139,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -2164,10 +2153,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B95" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C95">
         <v>2</v>
@@ -2178,10 +2167,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -2192,10 +2181,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B97" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -2251,7 +2240,7 @@
         <v>26</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C101">
         <v>3</v>
@@ -2262,10 +2251,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B102" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C102">
         <v>3</v>
@@ -2276,10 +2265,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>38</v>
+      </c>
+      <c r="B103" t="s">
         <v>42</v>
-      </c>
-      <c r="B103" t="s">
-        <v>47</v>
       </c>
       <c r="C103">
         <v>3</v>
@@ -2290,10 +2279,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C104">
         <v>3</v>
@@ -2304,10 +2293,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B105" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C105">
         <v>3</v>
@@ -2318,10 +2307,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C106">
         <v>3</v>
@@ -2332,10 +2321,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B107" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C107">
         <v>3</v>
@@ -2346,10 +2335,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B108" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C108">
         <v>3</v>
@@ -2360,10 +2349,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B109" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C109">
         <v>3</v>
@@ -2374,10 +2363,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B110" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C110">
         <v>3</v>
@@ -2388,10 +2377,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C111">
         <v>3</v>
@@ -2402,10 +2391,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C112">
         <v>3</v>
@@ -2416,10 +2405,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B113" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -2444,10 +2433,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C115">
         <v>4</v>
@@ -2458,10 +2447,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B116" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C116">
         <v>4</v>
@@ -2472,10 +2461,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B117" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C117">
         <v>4</v>
@@ -2486,10 +2475,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C118">
         <v>4</v>
@@ -2500,10 +2489,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B119" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C119">
         <v>4</v>
@@ -2514,10 +2503,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C120">
         <v>4</v>
@@ -2528,10 +2517,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B121" t="s">
         <v>109</v>
-      </c>
-      <c r="B121" t="s">
-        <v>124</v>
       </c>
       <c r="C121">
         <v>4</v>
@@ -2545,7 +2534,7 @@
         <v>3</v>
       </c>
       <c r="B122" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C122">
         <v>5</v>
@@ -2556,10 +2545,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B123" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C123">
         <v>5</v>
@@ -2570,10 +2559,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B124" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C124">
         <v>5</v>
@@ -2584,10 +2573,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C125">
         <v>5</v>
@@ -2601,7 +2590,7 @@
         <v>3</v>
       </c>
       <c r="B126" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C126">
         <v>6</v>
@@ -2612,10 +2601,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B127" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C127">
         <v>6</v>
@@ -2629,7 +2618,7 @@
         <v>3</v>
       </c>
       <c r="B128" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C128">
         <v>7</v>
